--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536308_LIGAREGULARB_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536308_LIGAREGULARB_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,7 +712,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>P. CARRENO VIDAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -724,64 +724,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4152</v>
+        <v>2.4872</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1179</v>
+        <v>0.8276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2973</v>
+        <v>1.6596</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4233</v>
+        <v>2.9013</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6282</v>
+        <v>1.229</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2049</v>
+        <v>1.6723</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3981</v>
+        <v>3.5551</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5548</v>
+        <v>1.897</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1567</v>
+        <v>1.6581</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0251</v>
+        <v>-0.6538</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07340000000000001</v>
+        <v>-0.668</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0483</v>
+        <v>0.0142</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2055</v>
+        <v>-1.6439</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2055</v>
+        <v>-3.2877</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.6439</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2591</v>
+        <v>1.3393</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2528</v>
+        <v>0.4301</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5119</v>
+        <v>0.9092</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9384</v>
+        <v>-0.1096</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1781</v>
+        <v>0.1301</v>
       </c>
       <c r="X4" t="n">
         <v>-0.2397</v>
@@ -795,7 +795,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CARRENO VIDAL</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,64 +807,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3036</v>
+        <v>1.4152</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3559</v>
+        <v>1.1179</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6596</v>
+        <v>0.2973</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7178</v>
+        <v>0.4233</v>
       </c>
       <c r="H5" t="n">
-        <v>1.229</v>
+        <v>0.6282</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4887</v>
+        <v>-0.2049</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3716</v>
+        <v>0.3981</v>
       </c>
       <c r="K5" t="n">
-        <v>1.897</v>
+        <v>0.5548</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4746</v>
+        <v>-0.1567</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6538</v>
+        <v>0.0251</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.668</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0142</v>
+        <v>-0.0483</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6439</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2877</v>
+        <v>-0.2055</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6439</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3393</v>
+        <v>0.2591</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4301</v>
+        <v>-0.2528</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9092</v>
+        <v>0.5119</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1096</v>
+        <v>0.9384</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1301</v>
+        <v>1.1781</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2397</v>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. CARREÑO VIDAL</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,64 +890,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1836</v>
+        <v>1.154</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1836</v>
+        <v>1.8427</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.6887</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1836</v>
+        <v>-0.6558</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-2.1309</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1836</v>
+        <v>1.475</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1836</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-2.0991</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1836</v>
+        <v>2.9595</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.5162</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.0318</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.4844</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.2055</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.8219</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.0029</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.0056</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.0068</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.0068</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>K. KELIKI EBENGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,64 +973,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1671</v>
+        <v>0.3389</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1671</v>
+        <v>-0.6737</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.0126</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1671</v>
+        <v>-0.1819</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1671</v>
+        <v>-0.6866</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5046</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1671</v>
+        <v>-0.5918</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1671</v>
+        <v>-0.6707</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0789</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.4098</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.0159</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.4257</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.8219</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.8219</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.3769</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2191</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.4589</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.4589</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>G. MONTOYA SOLANILLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,64 +1056,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.154</v>
+        <v>0.1896</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8427</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6887</v>
+        <v>0.1896</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6558</v>
+        <v>0.1419</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1309</v>
+        <v>0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>1.475</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8604000000000001</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.0991</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.9595</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5162</v>
+        <v>0.1419</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0318</v>
+        <v>0.1419</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4844</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2055</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8219</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0477</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0029</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0056</v>
+        <v>0.0477</v>
       </c>
       <c r="V8" t="n">
-        <v>2.0068</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.0068</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5836</v>
+        <v>-0.2368</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5836</v>
+        <v>1.8848</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-2.1216</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5836</v>
+        <v>-0.6268</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5836</v>
+        <v>0.9518</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-1.5786</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5836</v>
+        <v>1.1885</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5836</v>
+        <v>1.1096</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0789</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1.8154</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-1.6575</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.9516</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.6962</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.2554</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.1781</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1781</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. KELIKI EBENGO</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,64 +1222,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3389</v>
+        <v>-0.3874</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6737</v>
+        <v>-1.9256</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0126</v>
+        <v>1.5382</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1819</v>
+        <v>-0.7926</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6866</v>
+        <v>0.511</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5046</v>
+        <v>-1.3036</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5918</v>
+        <v>0.5878</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6707</v>
+        <v>0.4694</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0789</v>
+        <v>0.1184</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4098</v>
+        <v>-1.3804</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0159</v>
+        <v>0.0416</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4257</v>
+        <v>-1.422</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8219</v>
+        <v>-3.0822</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-5.137</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8219</v>
+        <v>2.0548</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1578</v>
+        <v>1.1313</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3769</v>
+        <v>0.2675</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2191</v>
+        <v>0.8638</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4589</v>
+        <v>2.3561</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4589</v>
+        <v>2.3561</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. MONTOYA SOLANILLA</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1896</v>
+        <v>-4.063</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1.0124</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1896</v>
+        <v>-3.0506</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1419</v>
+        <v>-1.7129</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1419</v>
+        <v>-0.4257</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-1.2872</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.0958</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.7671</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.6713</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1419</v>
+        <v>-1.6171</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1419</v>
+        <v>0.3413</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-1.9584</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.2329</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0477</v>
+        <v>0.8622</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.3163</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0477</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.5959</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.5959</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,67 +1388,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2368</v>
+        <v>-4.2625</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8848</v>
+        <v>-6.1347</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1216</v>
+        <v>1.8722</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6268</v>
+        <v>-4.1339</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9518</v>
+        <v>0.3148</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5786</v>
+        <v>-4.4487</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1885</v>
+        <v>-3.3113</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1096</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0789</v>
+        <v>-3.39</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8154</v>
+        <v>-0.8226</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1578</v>
+        <v>0.2361</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6575</v>
+        <v>-1.0587</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6163999999999999</v>
+        <v>-1.8493</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.2877</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6163999999999999</v>
+        <v>1.4384</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9516</v>
+        <v>1.7207</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6962</v>
+        <v>0.2246</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2554</v>
+        <v>1.4961</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1781</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2397</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1781</v>
+        <v>-0.2397</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,150 +1471,146 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3874</v>
+        <v>8.8659</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9256</v>
+        <v>2.600499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5382</v>
+        <v>6.2653</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7926</v>
+        <v>2.438300000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>0.511</v>
+        <v>5.915100000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3036</v>
+        <v>-3.4769</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5878</v>
+        <v>9.817</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4694</v>
+        <v>5.786600000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1184</v>
+        <v>4.030399999999998</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3804</v>
+        <v>-7.379</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0416</v>
+        <v>0.1283999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.422</v>
+        <v>-7.5073</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.0822</v>
+        <v>-5.1371</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.137</v>
+        <v>-16.4385</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0548</v>
+        <v>11.3014</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1313</v>
+        <v>9.0989</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2675</v>
+        <v>2.9412</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8638</v>
+        <v>6.1577</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3561</v>
+        <v>2.4657</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3561</v>
+        <v>6.2807</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>play_by_play_2536308_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-3.8149</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. GARCIA RIERA</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>VIDAL GOLOSINAS CIUDAD MOLINA BASKET</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.6465</v>
+        <v>1.2802</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.596</v>
+        <v>1.2763</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0506</v>
+        <v>0.004</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2965</v>
+        <v>1.4916</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0093</v>
+        <v>-0.6388</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2872</v>
+        <v>2.1304</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6794</v>
+        <v>1.6927</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3506</v>
+        <v>-0.2021</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6713</v>
+        <v>1.8948</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6171</v>
+        <v>-0.2012</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3413</v>
+        <v>-0.4368</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9584</v>
+        <v>0.2356</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6163999999999999</v>
+        <v>1.4384</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2329</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6163999999999999</v>
+        <v>1.4384</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8622</v>
+        <v>-1.0606</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3163</v>
+        <v>-0.8959</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5459000000000001</v>
+        <v>-0.1648</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.5959</v>
+        <v>-0.589</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.4794</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.5959</v>
+        <v>-1.0685</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1625,79 +1621,79 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. COSTA I VAZQUEZ</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>VIDAL GOLOSINAS CIUDAD MOLINA BASKET</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.4296</v>
+        <v>0.4182</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.3018</v>
+        <v>-0.6501</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8722</v>
+        <v>1.0684</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.301</v>
+        <v>0.7643</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-1.034</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.4487</v>
+        <v>1.7983</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.4784</v>
+        <v>2.7118</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.0884</v>
+        <v>0.1074</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.39</v>
+        <v>2.6044</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8226</v>
+        <v>-1.9475</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2361</v>
+        <v>-1.1414</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0587</v>
+        <v>-0.8061</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8493</v>
+        <v>-1.0274</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.2877</v>
+        <v>-4.1096</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4384</v>
+        <v>3.0822</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7207</v>
+        <v>-2.0241</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2246</v>
+        <v>-1.6085</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4961</v>
+        <v>-0.4157</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.7055</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2397</v>
+        <v>2.3561</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2397</v>
+        <v>0.3493</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1708,86 +1704,90 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>VIDAL GOLOSINAS CIUDAD MOLINA BASKET</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.865999999999996</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.600599999999998</v>
+        <v>0.0373</v>
       </c>
       <c r="F16" t="n">
-        <v>6.265299999999999</v>
+        <v>0.0338</v>
       </c>
       <c r="G16" t="n">
-        <v>2.438399999999998</v>
+        <v>1.2136</v>
       </c>
       <c r="H16" t="n">
-        <v>5.915100000000001</v>
+        <v>1.435</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.4769</v>
+        <v>-0.2214</v>
       </c>
       <c r="J16" t="n">
-        <v>9.8171</v>
+        <v>1.5561</v>
       </c>
       <c r="K16" t="n">
-        <v>5.786700000000002</v>
+        <v>1.5561</v>
       </c>
       <c r="L16" t="n">
-        <v>4.030499999999998</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.379</v>
+        <v>-0.3425</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1283999999999999</v>
+        <v>-0.1211</v>
       </c>
       <c r="O16" t="n">
-        <v>-7.5073</v>
+        <v>-0.2214</v>
       </c>
       <c r="P16" t="n">
-        <v>-5.1371</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-16.4385</v>
+        <v>-1.0274</v>
       </c>
       <c r="R16" t="n">
-        <v>11.3014</v>
+        <v>1.0274</v>
       </c>
       <c r="S16" t="n">
-        <v>9.0989</v>
+        <v>0.0355</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9412</v>
+        <v>-0.0326</v>
       </c>
       <c r="U16" t="n">
-        <v>6.1577</v>
+        <v>0.068</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4657</v>
+        <v>-1.1781</v>
       </c>
       <c r="W16" t="n">
-        <v>6.2807</v>
+        <v>-0.4589</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.8149</v>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+        <v>-0.7192</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2536308_LIGAREGULARB_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2802</v>
+        <v>-0.1584</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2763</v>
+        <v>1.0577</v>
       </c>
       <c r="F17" t="n">
-        <v>0.004</v>
+        <v>-1.2161</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4916</v>
+        <v>0.1551</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6388</v>
+        <v>-1.0066</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1304</v>
+        <v>1.1617</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6927</v>
+        <v>2.2017</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2021</v>
+        <v>0.0296</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8948</v>
+        <v>2.1721</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2012</v>
+        <v>-2.0466</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4368</v>
+        <v>-1.0362</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2356</v>
+        <v>-1.0104</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4384</v>
+        <v>0.411</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0274</v>
       </c>
       <c r="R17" t="n">
         <v>1.4384</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0606</v>
+        <v>-1.3135</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8959</v>
+        <v>-0.3563</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1648</v>
+        <v>-0.9571</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.589</v>
+        <v>0.589</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4794</v>
+        <v>0.2397</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0685</v>
+        <v>0.3493</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4182</v>
+        <v>-0.9248</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6501</v>
+        <v>-1.0192</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0684</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7643</v>
+        <v>-1.3844</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.034</v>
+        <v>-1.5504</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7983</v>
+        <v>0.166</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7118</v>
+        <v>0.2365</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1074</v>
+        <v>-0.5142</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6044</v>
+        <v>0.7507</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9475</v>
+        <v>-1.6209</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1414</v>
+        <v>-1.0362</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8061</v>
+        <v>-0.5847</v>
       </c>
       <c r="P18" t="n">
+        <v>1.2329</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-1.0274</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-4.1096</v>
-      </c>
       <c r="R18" t="n">
-        <v>3.0822</v>
+        <v>2.2603</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.0241</v>
+        <v>-1.6021</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.6085</v>
+        <v>-1.0571</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4157</v>
+        <v>-0.5451</v>
       </c>
       <c r="V18" t="n">
-        <v>2.7055</v>
+        <v>0.8288</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3561</v>
+        <v>0.8288</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3493</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.9908</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0373</v>
+        <v>-1.5432</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0338</v>
+        <v>0.5524</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2136</v>
+        <v>-1.5402</v>
       </c>
       <c r="H19" t="n">
-        <v>1.435</v>
+        <v>-0.8148</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2214</v>
+        <v>-0.7255</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5561</v>
+        <v>-0.5249</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5561</v>
+        <v>-0.4465</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3425</v>
+        <v>-1.0154</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1211</v>
+        <v>-0.3682</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2214</v>
+        <v>-0.6471</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.0274</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0274</v>
+        <v>1.6439</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0355</v>
+        <v>-0.3068</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0326</v>
+        <v>-0.2307</v>
       </c>
       <c r="U19" t="n">
-        <v>0.068</v>
+        <v>-0.0761</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1781</v>
+        <v>0.2397</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.4589</v>
+        <v>0.2397</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7192</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>F. HERNANDEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,40 +2048,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1584</v>
+        <v>-1.2762</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0577</v>
+        <v>1.0432</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2161</v>
+        <v>-2.3194</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1551</v>
+        <v>2.4619</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0066</v>
+        <v>0.2838</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1617</v>
+        <v>2.1781</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2017</v>
+        <v>3.2148</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0296</v>
+        <v>0.8466</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1721</v>
+        <v>2.3683</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0466</v>
+        <v>-0.7529</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0362</v>
+        <v>-0.5628</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0104</v>
+        <v>-0.1902</v>
       </c>
       <c r="P20" t="n">
         <v>0.411</v>
@@ -2096,19 +2096,19 @@
         <v>-1.3135</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3563</v>
+        <v>-1.1442</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9571</v>
+        <v>-0.1692</v>
       </c>
       <c r="V20" t="n">
-        <v>0.589</v>
+        <v>-2.8356</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3493</v>
+        <v>-2.8356</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>G. CADME ARIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,64 +2131,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9248</v>
+        <v>-1.6653</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0192</v>
+        <v>-2.5409</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.8756</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3844</v>
+        <v>-2.7821</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5504</v>
+        <v>-1.363</v>
       </c>
       <c r="I21" t="n">
-        <v>0.166</v>
+        <v>-1.4191</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2365</v>
+        <v>-2.8188</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5142</v>
+        <v>-1.3997</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7507</v>
+        <v>-1.4191</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6209</v>
+        <v>0.0367</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0362</v>
+        <v>0.0367</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5847</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2329</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2603</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6021</v>
+        <v>0.5004</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0571</v>
+        <v>0.2779</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5451</v>
+        <v>0.2225</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8288</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8288</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>K. ABOUBACAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,64 +2214,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9908</v>
+        <v>-2.286</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5432</v>
+        <v>-1.6899</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5524</v>
+        <v>-0.5961</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5402</v>
+        <v>-0.9822</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8148</v>
+        <v>-0.1154</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7255</v>
+        <v>-0.8668</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5249</v>
+        <v>-0.0194</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4465</v>
+        <v>0.0584</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0154</v>
+        <v>-0.9628</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3682</v>
+        <v>-0.1737</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6471</v>
+        <v>-0.789</v>
       </c>
       <c r="P22" t="n">
+        <v>-1.4384</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-2.0548</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.6163999999999999</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.0274</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.6439</v>
-      </c>
       <c r="S22" t="n">
-        <v>-0.3068</v>
+        <v>0.1345</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2307</v>
+        <v>0.3843</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0761</v>
+        <v>-0.2498</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. HERNANDEZ MARTINEZ</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2762</v>
+        <v>-3.016</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0432</v>
+        <v>-2.2364</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3194</v>
+        <v>-0.7796</v>
       </c>
       <c r="G23" t="n">
-        <v>2.4619</v>
+        <v>-1.8358</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2838</v>
+        <v>-1.111</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1781</v>
+        <v>-0.7249</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2148</v>
+        <v>-0.8719</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8466</v>
+        <v>-0.164</v>
       </c>
       <c r="L23" t="n">
-        <v>2.3683</v>
+        <v>-0.7078</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7529</v>
+        <v>-0.9639</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5628</v>
+        <v>-0.9469</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1902</v>
+        <v>-0.017</v>
       </c>
       <c r="P23" t="n">
-        <v>0.411</v>
+        <v>2.8767</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0274</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4384</v>
+        <v>2.8767</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3135</v>
+        <v>-1.8309</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1442</v>
+        <v>-1.4946</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1692</v>
+        <v>-0.3362</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.8356</v>
+        <v>-2.226</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1301</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.8356</v>
+        <v>-2.3561</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. CADME ARIAS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,318 +2380,69 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.6653</v>
+        <v>-8.5481</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5409</v>
+        <v>-6.2652</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8756</v>
+        <v>-2.2827</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.7821</v>
+        <v>-2.4382</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.363</v>
+        <v>-5.9152</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4191</v>
+        <v>3.476800000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.8188</v>
+        <v>7.378600000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3997</v>
+        <v>-0.1283999999999997</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4191</v>
+        <v>7.5073</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0367</v>
+        <v>-9.817</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0367</v>
+        <v>-5.786600000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>-4.0303</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6163999999999999</v>
+        <v>5.137</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-11.3014</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6163999999999999</v>
+        <v>16.4385</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5004</v>
+        <v>-8.7811</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2779</v>
+        <v>-6.1577</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2225</v>
+        <v>-2.6235</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-2.4657</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.8149</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>play_by_play_2536308_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>K. ABOUBACAR</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>VIDAL GOLOSINAS CIUDAD MOLINA BASKET</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-2.286</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-1.6899</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-0.5961</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-0.9822</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-0.1154</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-0.8668</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-0.0194</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.0584</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-0.07779999999999999</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-0.9628</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-0.1737</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-0.789</v>
-      </c>
-      <c r="P25" t="n">
-        <v>-1.4384</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-2.0548</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.6163999999999999</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.1345</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.3843</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-0.2498</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536308_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>J. SOLARIN</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>VIDAL GOLOSINAS CIUDAD MOLINA BASKET</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-3.016</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-2.2364</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.7796</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-1.8358</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-1.111</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-0.7249</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-0.8719</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-0.164</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-0.7078</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-0.9639</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-0.9469</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-0.017</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.8767</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.8767</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-1.8309</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-1.4946</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-0.3362</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-2.226</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.1301</v>
-      </c>
-      <c r="X26" t="n">
-        <v>-2.3561</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536308_LIGAREGULARB_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>VIDAL GOLOSINAS CIUDAD MOLINA BASKET</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-8.5481</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-6.2652</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-2.2827</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-2.4382</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-5.9152</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3.476800000000001</v>
-      </c>
-      <c r="J27" t="n">
-        <v>7.378600000000002</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-0.1283999999999997</v>
-      </c>
-      <c r="L27" t="n">
-        <v>7.5073</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-9.817</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-5.786600000000001</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-4.0303</v>
-      </c>
-      <c r="P27" t="n">
-        <v>5.137</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-11.3014</v>
-      </c>
-      <c r="R27" t="n">
-        <v>16.4385</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-8.7811</v>
-      </c>
-      <c r="T27" t="n">
-        <v>-6.1577</v>
-      </c>
-      <c r="U27" t="n">
-        <v>-2.6235</v>
-      </c>
-      <c r="V27" t="n">
-        <v>-2.4657</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3.8149</v>
-      </c>
-      <c r="X27" t="n">
         <v>-6.280799999999999</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
